--- a/Resources/Data/EnemySpawnData.xlsx
+++ b/Resources/Data/EnemySpawnData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it242225\Documents\Visual Studio 2022\projects\二年生\オリジナル_テスト\CaveDiving\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF9A06E-6DA4-4CED-A628-1B0BFA2A671A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7E94D0-38FE-49D3-9675-98FAF472C66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="1392" windowWidth="19212" windowHeight="10692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,105 +29,42 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
-  <si>
-    <t>効果</t>
-    <rPh sb="0" eb="2">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>効果説明</t>
-    <rPh sb="0" eb="2">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>体力</t>
-  </si>
-  <si>
-    <t>体力</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃力</t>
-  </si>
-  <si>
-    <t>防御力</t>
-  </si>
-  <si>
-    <t>特殊</t>
-  </si>
-  <si>
-    <t>強化項目</t>
-    <rPh sb="0" eb="2">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宝石の種類</t>
-    <rPh sb="0" eb="2">
-      <t>ホウセキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エメラルド</t>
-  </si>
-  <si>
-    <t>ルビー</t>
-  </si>
-  <si>
-    <t>サファイア</t>
-  </si>
-  <si>
-    <t>ダイヤ</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>パネル画像ファイルパス</t>
-    <rPh sb="3" eb="5">
-      <t>ガゾウ</t>
+    <t>X座標</t>
+    <rPh sb="1" eb="3">
+      <t>ザヒョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>emeraldpanel.png</t>
+    <t>Y座標</t>
+    <rPh sb="1" eb="3">
+      <t>ザヒョウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>rubypanel.png</t>
-  </si>
-  <si>
-    <t>rubypanel.png</t>
+    <t>Z座標</t>
+    <rPh sb="1" eb="3">
+      <t>ザヒョウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>sapphirepanel.png</t>
-  </si>
-  <si>
-    <t>frame.png</t>
-    <phoneticPr fontId="1"/>
+    <t>コウモリ</t>
   </si>
 </sst>
 </file>
@@ -158,7 +95,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -181,25 +118,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -480,192 +407,164 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="13.19921875" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="2" max="4" width="13.69921875" customWidth="1"/>
+    <col min="5" max="7" width="9.296875" customWidth="1"/>
+    <col min="8" max="8" width="12.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-8</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-10</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-40</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="str">
-        <f>CONCATENATE(C2,"を",D2,"増加する")</f>
-        <v>体力を10増加する</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="str">
-        <f t="shared" ref="E3:E8" si="0">CONCATENATE(C3,"を",D3,"増加する")</f>
-        <v>攻撃力を10増加する</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>防御力を10増加する</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>体力を10増加する</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>攻撃力を10増加する</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
+      <c r="C7" s="1">
+        <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
       </c>
-      <c r="E7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>防御力を10増加する</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>特殊を10増加する</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8" xr:uid="{3656DD66-B663-4BAF-9823-A65DEC9D1361}">
-      <formula1>"体力,攻撃力,防御力,特殊"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B8" xr:uid="{99318863-A0A4-4C5C-A7B2-83B80F5A2DDE}">
-      <formula1>"エメラルド,ルビー,サファイア,ダイヤ"</formula1>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A8" xr:uid="{098535F7-4E2D-487C-A3A4-1565CF02C612}">
+      <formula1>"コウモリ,ゴーレム"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
